--- a/4_analisis/salidas/funciones/tablas_funciones.xlsx
+++ b/4_analisis/salidas/funciones/tablas_funciones.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Peso de las funciones en 2026 (euros corrientes)</t>
+          <t>Peso de las funciones en 2027 (euros corrientes)</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Importe 2026 (M€)</t>
+          <t>Importe 2027 (M€)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4542</v>
+        <v>4927.5</v>
       </c>
       <c r="D5" t="n">
-        <v>38.14</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="6">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2609.4</v>
+        <v>2848.4</v>
       </c>
       <c r="D6" t="n">
-        <v>21.91</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="7">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1148.4</v>
+        <v>1219.9</v>
       </c>
       <c r="D7" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>839.6</v>
+        <v>1037</v>
       </c>
       <c r="D8" t="n">
-        <v>7.05</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="9">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>487.3</v>
+        <v>393</v>
       </c>
       <c r="D9" t="n">
-        <v>4.09</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="10">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>367.2</v>
+        <v>356.6</v>
       </c>
       <c r="D10" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Industria y Energía</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Actuaciones de carácter económico</t>
+          <t>Servicios públicos básicos</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>291.2</v>
+        <v>237.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="12">
@@ -616,52 +616,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>221.4</v>
+        <v>165.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Acceso a la vivienda y fomento de la edificación</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Servicios públicos básicos</t>
+          <t>Actuaciones de protección y promoción social</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>216.8</v>
+        <v>162.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Acceso a la vivienda y fomento de la edificación</t>
+          <t>Deuda Pública</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Actuaciones de protección y promoción social</t>
+          <t>Actuaciones de carácter general</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170.2</v>
+        <v>150.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agricultura, Pesca y Alimentación</t>
+          <t>Subvenciones al transporte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,52 +670,52 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>130.7</v>
+        <v>145.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Otras actuaciones de carácter económico</t>
+          <t>Alta Dirección</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Actuaciones de carácter económico</t>
+          <t>Actuaciones de carácter general</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>116.7</v>
+        <v>129.8</v>
       </c>
       <c r="D16" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Administración Financiera y Tributaria</t>
+          <t>Agricultura, Pesca y Alimentación</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Actuaciones de carácter general</t>
+          <t>Actuaciones de carácter económico</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>109.1</v>
+        <v>126.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Subvenciones al transporte</t>
+          <t>Otras actuaciones de carácter económico</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>108.6</v>
+        <v>115.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alta Dirección</t>
+          <t>Administración Financiera y Tributaria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,64 +742,64 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105.8</v>
+        <v>109.7</v>
       </c>
       <c r="D19" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deuda Pública</t>
+          <t>Fomento del Empleo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Actuaciones de carácter general</t>
+          <t>Actuaciones de protección y promoción social</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>104.6</v>
+        <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fomento del Empleo</t>
+          <t>Investigación, desarrollo e innovación</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Actuaciones de protección y promoción social</t>
+          <t>Actuaciones de carácter económico</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>96.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Investigación, desarrollo e innovación</t>
+          <t>Seguridad ciudadana e instituciones penitenciarias</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Actuaciones de carácter económico</t>
+          <t>Servicios públicos básicos</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>91.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="23">
@@ -814,28 +814,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>72.7</v>
+        <v>75.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Seguridad ciudadana e instituciones penitenciarias</t>
+          <t>Industria y Energía</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Servicios públicos básicos</t>
+          <t>Actuaciones de carácter económico</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>66.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="25">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>0.11</v>
@@ -893,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Composición por capítulos del cambio 2023→2026</t>
+          <t>Composición por capítulos del cambio 2023→2027</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>52,0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>78,4</t>
+          <t>98,2</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54,6</t>
+          <t>31,3</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-9,4</t>
+          <t>-7,1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-33,3</t>
+          <t>-13,5</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-9,2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-6,5</t>
+          <t>-17,4</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>1,4</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>-0,4</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>14,0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>5,9</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>81,3</t>
+          <t>252,5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>90,5</t>
+          <t>105,9</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-8,2</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>1,1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>-29,9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>-12,5</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>173,1</t>
+          <t>303,8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>25,5</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30,0</t>
+          <t>54,9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>708,3</t>
+          <t>987,5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>87,1</t>
+          <t>82,8</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-51,3</t>
+          <t>-72,0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-6,3</t>
+          <t>-6,0</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-47,3</t>
+          <t>-81,0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-5,8</t>
+          <t>-6,8</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>-1,5</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-7,6</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-81,4</t>
+          <t>-104,3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-50,2</t>
+          <t>49,8</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>244,9</t>
+          <t>-122,7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>151,0</t>
+          <t>58,5</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>4,0</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51,2</t>
+          <t>91,8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>24,8</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>158,2</t>
+          <t>192,7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>53,0</t>
+          <t>52,1</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>54,1</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,7</t>
         </is>
       </c>
     </row>
